--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-13).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-13).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-173</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 1.662.167,59</t>
-  </si>
-  <si>
-    <t>R$ 9.033,52
-R$ 9.198,34</t>
-  </si>
-  <si>
-    <t>(2.9%)
-(1.1%)</t>
-  </si>
-  <si>
-    <t>99.5</t>
-  </si>
-  <si>
-    <t>(7.8%)</t>
+174</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 1.667.279,52</t>
+  </si>
+  <si>
+    <t>R$ 9.012,32
+R$ 9.174,85</t>
+  </si>
+  <si>
+    <t>(3.1%)
+(1.4%)</t>
+  </si>
+  <si>
+    <t>99.4</t>
+  </si>
+  <si>
+    <t>(7.9%)</t>
   </si>
   <si>
     <t>14.1%</t>
   </si>
   <si>
-    <t>(27.9%)</t>
+    <t>(27.8%)</t>
   </si>
   <si>
     <t>2.5%</t>
@@ -950,7 +950,7 @@
     <t>30.0</t>
   </si>
   <si>
-    <t>57.3%</t>
+    <t>57.2%</t>
   </si>
   <si>
     <t>16.4%</t>
@@ -968,13 +968,13 @@
     <t>21.5</t>
   </si>
   <si>
-    <t>61.1%</t>
+    <t>61.0%</t>
   </si>
   <si>
     <t>-R$ 53.650,26</t>
   </si>
   <si>
-    <t>2.97</t>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -6646,7 +6646,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6682,25 +6682,59 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
+      <c r="O42" s="5">
+        <v>5111.9300000000003</v>
+      </c>
+      <c r="P42" s="5">
+        <v>5111.9300000000003</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-0.44778278294498275</v>
+      </c>
+      <c r="R42" s="7">
+        <v>63</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.33684210526315794</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.39551300585101906</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.072255449507328928</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.046837887060268819</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.012547511409585028</v>
+      </c>
+      <c r="X42" s="8">
+        <v>29.893711320754718</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.39622641509433965</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.094339622641509441</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>6.7954306451612911</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>10.489795918367347</v>
+      </c>
       <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="AD42" s="8">
+        <v>23.158805660377357</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.49056603773584906</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -15353,7 +15387,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15706,7 +15740,7 @@
         <v>-108.7</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">

--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-13).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-13).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-174</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 1.667.279,52</t>
-  </si>
-  <si>
-    <t>R$ 9.012,32
-R$ 9.174,85</t>
+175</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 1.677.468,22</t>
+  </si>
+  <si>
+    <t>R$ 9.018,65
+R$ 9.180,65</t>
   </si>
   <si>
     <t>(3.1%)
 (1.4%)</t>
   </si>
   <si>
-    <t>99.4</t>
+    <t>99.5</t>
   </si>
   <si>
     <t>(7.9%)</t>
   </si>
   <si>
-    <t>14.1%</t>
-  </si>
-  <si>
-    <t>(27.8%)</t>
+    <t>14.3%</t>
+  </si>
+  <si>
+    <t>(27.6%)</t>
   </si>
   <si>
     <t>2.5%</t>
@@ -950,10 +950,10 @@
     <t>30.0</t>
   </si>
   <si>
-    <t>57.2%</t>
-  </si>
-  <si>
-    <t>16.4%</t>
+    <t>57.0%</t>
+  </si>
+  <si>
+    <t>16.3%</t>
   </si>
   <si>
     <t>6.7</t>
@@ -962,16 +962,16 @@
     <t>8.1</t>
   </si>
   <si>
-    <t>15.0</t>
+    <t>14.9</t>
   </si>
   <si>
     <t>21.5</t>
   </si>
   <si>
-    <t>61.0%</t>
-  </si>
-  <si>
-    <t>-R$ 53.650,26</t>
+    <t>61.2%</t>
+  </si>
+  <si>
+    <t>-R$ 53.905,86</t>
   </si>
   <si>
     <t>2.95</t>
@@ -6724,7 +6724,9 @@
       <c r="AB42" s="8">
         <v>10.489795918367347</v>
       </c>
-      <c r="AC42" s="8"/>
+      <c r="AC42" s="8">
+        <v>17.379859</v>
+      </c>
       <c r="AD42" s="8">
         <v>23.158805660377357</v>
       </c>
@@ -8692,7 +8694,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8728,25 +8730,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="O58" s="5">
+        <v>10188.700000000001</v>
+      </c>
+      <c r="P58" s="5">
+        <v>10188.700000000001</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>-0.041503761096080005</v>
+      </c>
+      <c r="R58" s="7">
+        <v>122</v>
+      </c>
+      <c r="S58" s="6">
+        <v>-0.068702290076335881</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.31554474074219474</v>
+      </c>
+      <c r="U58" s="6">
+        <v>-0.037630836122370857</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.011861523059860433</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.00063467370714615206</v>
+      </c>
+      <c r="X58" s="8">
+        <v>24.985284042553193</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.34042553191489361</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.021276595744680851</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>2.721311475409836</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>6.6842202127659567</v>
+      </c>
+      <c r="AC58" s="8">
+        <v>9.4840409999999995</v>
+      </c>
+      <c r="AD58" s="8">
+        <v>16.371808510638299</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.7978723404255319</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>-255.59999999999999</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -15375,7 +15413,9 @@
       <c r="AB111" s="8">
         <v>1.8015857142857143</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>10.566666</v>
+      </c>
       <c r="AD111" s="8">
         <v>17.519047619047619</v>
       </c>
@@ -16877,7 +16917,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17270,7 +17310,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18447,7 +18487,7 @@
         <v>0</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -20765,7 +20805,7 @@
         <v>-3077.5</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -21977,7 +22017,7 @@
         <v>-656.5</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -24019,7 +24059,9 @@
       <c r="AB179" s="8">
         <v>1.3242244186046512</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>6.0209669999999997</v>
+      </c>
       <c r="AD179" s="8">
         <v>12.965697674418605</v>
       </c>
@@ -28100,7 +28142,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
